--- a/GearSage-client/pkgGear/data_raw/experiment_reports/review/2026-04-16_shimano_baitcasting_reel_whitelist_review_filled.xlsx
+++ b/GearSage-client/pkgGear/data_raw/experiment_reports/review/2026-04-16_shimano_baitcasting_reel_whitelist_review_filled.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:T31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -448,15 +448,21 @@
         <v>review_status</v>
       </c>
       <c r="O1" t="str">
+        <v>approved_value_raw</v>
+      </c>
+      <c r="P1" t="str">
         <v>approved_value</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
+        <v>body_material_tech</v>
+      </c>
+      <c r="R1" t="str">
         <v>reviewer</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="S1" t="str">
         <v>review_note</v>
       </c>
-      <c r="R1" t="str">
+      <c r="T1" t="str">
         <v>rejected_candidate_reason</v>
       </c>
     </row>
@@ -507,12 +513,18 @@
         <v>Hagane aluminum alloy body</v>
       </c>
       <c r="P2" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Aluminum alloy</v>
       </c>
       <c r="Q2" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="R2" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S2" t="str">
         <v>Correct and acceptable, but this appears to describe the 2021 ANTARES DC generation.</v>
       </c>
-      <c r="R2" t="str">
+      <c r="T2" t="str">
         <v/>
       </c>
     </row>
@@ -563,12 +575,18 @@
         <v>Hagane aluminum alloy body</v>
       </c>
       <c r="P3" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Aluminum alloy</v>
       </c>
       <c r="Q3" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="R3" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S3" t="str">
         <v>Correct and acceptable, but this appears to describe the 2021 ANTARES DC generation.</v>
       </c>
-      <c r="R3" t="str">
+      <c r="T3" t="str">
         <v/>
       </c>
     </row>
@@ -619,12 +637,18 @@
         <v>Hagane aluminum alloy body</v>
       </c>
       <c r="P4" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Aluminum alloy</v>
       </c>
       <c r="Q4" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="R4" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S4" t="str">
         <v>Correct and acceptable, but this appears to describe the 2021 ANTARES DC generation.</v>
       </c>
-      <c r="R4" t="str">
+      <c r="T4" t="str">
         <v/>
       </c>
     </row>
@@ -675,12 +699,18 @@
         <v>Hagane aluminum alloy body</v>
       </c>
       <c r="P5" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Aluminum alloy</v>
       </c>
       <c r="Q5" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="R5" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S5" t="str">
         <v>Correct and acceptable, but this appears to describe the 2021 ANTARES DC generation.</v>
       </c>
-      <c r="R5" t="str">
+      <c r="T5" t="str">
         <v/>
       </c>
     </row>
@@ -731,12 +761,18 @@
         <v>Hagane aluminum alloy body</v>
       </c>
       <c r="P6" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Aluminum alloy</v>
       </c>
       <c r="Q6" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="R6" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S6" t="str">
         <v>Correct and acceptable, but this appears to describe the 2021 ANTARES DC generation.</v>
       </c>
-      <c r="R6" t="str">
+      <c r="T6" t="str">
         <v/>
       </c>
     </row>
@@ -787,12 +823,18 @@
         <v>Hagane aluminum alloy body</v>
       </c>
       <c r="P7" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Aluminum alloy</v>
       </c>
       <c r="Q7" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="R7" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S7" t="str">
         <v>Correct and acceptable, but this appears to describe the 2021 ANTARES DC generation.</v>
       </c>
-      <c r="R7" t="str">
+      <c r="T7" t="str">
         <v/>
       </c>
     </row>
@@ -843,12 +885,18 @@
         <v>Magnesium</v>
       </c>
       <c r="P8" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Magnesium</v>
       </c>
       <c r="Q8" t="str">
+        <v/>
+      </c>
+      <c r="R8" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S8" t="str">
         <v>Reject candidate 'metal frames' because it is not a specific material.</v>
       </c>
-      <c r="R8" t="str">
+      <c r="T8" t="str">
         <v>Candidate is generic wording, not an explicit material field.</v>
       </c>
     </row>
@@ -899,12 +947,18 @@
         <v>Magnesium</v>
       </c>
       <c r="P9" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Magnesium</v>
       </c>
       <c r="Q9" t="str">
+        <v/>
+      </c>
+      <c r="R9" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S9" t="str">
         <v>Reject candidate 'metal frames' because it is not a specific material.</v>
       </c>
-      <c r="R9" t="str">
+      <c r="T9" t="str">
         <v>Candidate is generic wording, not an explicit material field.</v>
       </c>
     </row>
@@ -955,12 +1009,18 @@
         <v>Magnesium</v>
       </c>
       <c r="P10" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Magnesium</v>
       </c>
       <c r="Q10" t="str">
+        <v/>
+      </c>
+      <c r="R10" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S10" t="str">
         <v>Reject candidate 'metal frames' because it is not a specific material.</v>
       </c>
-      <c r="R10" t="str">
+      <c r="T10" t="str">
         <v>Candidate is generic wording, not an explicit material field.</v>
       </c>
     </row>
@@ -1011,12 +1071,18 @@
         <v>Magnesium</v>
       </c>
       <c r="P11" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Magnesium</v>
       </c>
       <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S11" t="str">
         <v>Reject candidate 'metal frames' because it is not a specific material.</v>
       </c>
-      <c r="R11" t="str">
+      <c r="T11" t="str">
         <v>Candidate is generic wording, not an explicit material field.</v>
       </c>
     </row>
@@ -1067,12 +1133,18 @@
         <v>CORESOLID BODY 镁合金一体成型</v>
       </c>
       <c r="P12" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Magnesium</v>
       </c>
       <c r="Q12" t="str">
+        <v>CORESOLID BODY / 一体成型</v>
+      </c>
+      <c r="R12" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S12" t="str">
         <v>Reject candidate 'Core solid metal body' because it is a technology phrase, not a precise material expression.</v>
       </c>
-      <c r="R12" t="str">
+      <c r="T12" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
     </row>
@@ -1123,12 +1195,18 @@
         <v>Duralumin drive gear</v>
       </c>
       <c r="P13" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Duralumin drive gear</v>
       </c>
       <c r="Q13" t="str">
+        <v/>
+      </c>
+      <c r="R13" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S13" t="str">
         <v>Correct and acceptable, but keep year awareness for other Metanium DC generations.</v>
       </c>
-      <c r="R13" t="str">
+      <c r="T13" t="str">
         <v/>
       </c>
     </row>
@@ -1179,12 +1257,18 @@
         <v>CORESOLID BODY 镁合金一体成型</v>
       </c>
       <c r="P14" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Magnesium</v>
       </c>
       <c r="Q14" t="str">
+        <v>CORESOLID BODY / 一体成型</v>
+      </c>
+      <c r="R14" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S14" t="str">
         <v>Reject candidate 'Core solid metal body' because it is a technology phrase, not a precise material expression.</v>
       </c>
-      <c r="R14" t="str">
+      <c r="T14" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
     </row>
@@ -1235,12 +1319,18 @@
         <v>Duralumin drive gear</v>
       </c>
       <c r="P15" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Duralumin drive gear</v>
       </c>
       <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S15" t="str">
         <v>Correct and acceptable, but keep year awareness for other Metanium DC generations.</v>
       </c>
-      <c r="R15" t="str">
+      <c r="T15" t="str">
         <v/>
       </c>
     </row>
@@ -1291,12 +1381,18 @@
         <v>CORESOLID BODY 镁合金一体成型</v>
       </c>
       <c r="P16" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Magnesium</v>
       </c>
       <c r="Q16" t="str">
+        <v>CORESOLID BODY / 一体成型</v>
+      </c>
+      <c r="R16" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S16" t="str">
         <v>Reject candidate 'Core solid metal body' because it is a technology phrase, not a precise material expression.</v>
       </c>
-      <c r="R16" t="str">
+      <c r="T16" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
     </row>
@@ -1347,12 +1443,18 @@
         <v>Duralumin drive gear</v>
       </c>
       <c r="P17" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Duralumin drive gear</v>
       </c>
       <c r="Q17" t="str">
+        <v/>
+      </c>
+      <c r="R17" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S17" t="str">
         <v>Correct and acceptable, but keep year awareness for other Metanium DC generations.</v>
       </c>
-      <c r="R17" t="str">
+      <c r="T17" t="str">
         <v/>
       </c>
     </row>
@@ -1403,12 +1505,18 @@
         <v>CORESOLID BODY 镁合金一体成型</v>
       </c>
       <c r="P18" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Magnesium</v>
       </c>
       <c r="Q18" t="str">
+        <v>CORESOLID BODY / 一体成型</v>
+      </c>
+      <c r="R18" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S18" t="str">
         <v>Reject candidate 'Core solid metal body' because it is a technology phrase, not a precise material expression.</v>
       </c>
-      <c r="R18" t="str">
+      <c r="T18" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
     </row>
@@ -1459,12 +1567,18 @@
         <v>Duralumin drive gear</v>
       </c>
       <c r="P19" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Duralumin drive gear</v>
       </c>
       <c r="Q19" t="str">
+        <v/>
+      </c>
+      <c r="R19" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S19" t="str">
         <v>Correct and acceptable, but keep year awareness for other Metanium DC generations.</v>
       </c>
-      <c r="R19" t="str">
+      <c r="T19" t="str">
         <v/>
       </c>
     </row>
@@ -1515,12 +1629,18 @@
         <v>CORESOLID BODY 镁合金一体成型</v>
       </c>
       <c r="P20" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Magnesium</v>
       </c>
       <c r="Q20" t="str">
+        <v>CORESOLID BODY / 一体成型</v>
+      </c>
+      <c r="R20" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S20" t="str">
         <v>Reject candidate 'Core solid metal body' because it is a technology phrase, not a precise material expression.</v>
       </c>
-      <c r="R20" t="str">
+      <c r="T20" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
     </row>
@@ -1571,12 +1691,18 @@
         <v>Duralumin drive gear</v>
       </c>
       <c r="P21" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Duralumin drive gear</v>
       </c>
       <c r="Q21" t="str">
+        <v/>
+      </c>
+      <c r="R21" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S21" t="str">
         <v>Correct and acceptable, but keep year awareness for other Metanium DC generations.</v>
       </c>
-      <c r="R21" t="str">
+      <c r="T21" t="str">
         <v/>
       </c>
     </row>
@@ -1627,12 +1753,18 @@
         <v>CORESOLID BODY 镁合金一体成型</v>
       </c>
       <c r="P22" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Magnesium</v>
       </c>
       <c r="Q22" t="str">
+        <v>CORESOLID BODY / 一体成型</v>
+      </c>
+      <c r="R22" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S22" t="str">
         <v>Reject candidate 'Core solid metal body' because it is a technology phrase, not a precise material expression.</v>
       </c>
-      <c r="R22" t="str">
+      <c r="T22" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
     </row>
@@ -1683,12 +1815,18 @@
         <v>Duralumin drive gear</v>
       </c>
       <c r="P23" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Duralumin drive gear</v>
       </c>
       <c r="Q23" t="str">
+        <v/>
+      </c>
+      <c r="R23" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S23" t="str">
         <v>Correct and acceptable, but keep year awareness for other Metanium DC generations.</v>
       </c>
-      <c r="R23" t="str">
+      <c r="T23" t="str">
         <v/>
       </c>
     </row>
@@ -1739,12 +1877,18 @@
         <v>Fully machined aluminum body and side plates</v>
       </c>
       <c r="P24" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Aluminum</v>
       </c>
       <c r="Q24" t="str">
+        <v>全加工</v>
+      </c>
+      <c r="R24" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S24" t="str">
         <v>Correct and acceptable, but keep year awareness for future generations.</v>
       </c>
-      <c r="R24" t="str">
+      <c r="T24" t="str">
         <v/>
       </c>
     </row>
@@ -1795,12 +1939,18 @@
         <v>Fully machined aluminum body and side plates</v>
       </c>
       <c r="P25" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Aluminum</v>
       </c>
       <c r="Q25" t="str">
+        <v>全加工</v>
+      </c>
+      <c r="R25" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S25" t="str">
         <v>Correct and acceptable, but keep year awareness for future generations.</v>
       </c>
-      <c r="R25" t="str">
+      <c r="T25" t="str">
         <v/>
       </c>
     </row>
@@ -1851,12 +2001,18 @@
         <v>Fully machined aluminum body and side plates</v>
       </c>
       <c r="P26" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Aluminum</v>
       </c>
       <c r="Q26" t="str">
+        <v>全加工</v>
+      </c>
+      <c r="R26" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S26" t="str">
         <v>Correct and acceptable, but keep year awareness for future generations.</v>
       </c>
-      <c r="R26" t="str">
+      <c r="T26" t="str">
         <v/>
       </c>
     </row>
@@ -1907,12 +2063,18 @@
         <v>Fully machined aluminum body and side plates</v>
       </c>
       <c r="P27" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Aluminum</v>
       </c>
       <c r="Q27" t="str">
+        <v>全加工</v>
+      </c>
+      <c r="R27" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S27" t="str">
         <v>Correct and acceptable, but keep year awareness for future generations.</v>
       </c>
-      <c r="R27" t="str">
+      <c r="T27" t="str">
         <v/>
       </c>
     </row>
@@ -1963,12 +2125,18 @@
         <v>镁合金 (Magnesium) HAGANE 机身</v>
       </c>
       <c r="P28" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Magnesium</v>
       </c>
       <c r="Q28" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="R28" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S28" t="str">
         <v>Reject candidate 'Hagane body system' because it is a technology/system term, not the actual material wording.</v>
       </c>
-      <c r="R28" t="str">
+      <c r="T28" t="str">
         <v>Candidate is a technology/system phrase instead of a specific body material.</v>
       </c>
     </row>
@@ -2019,12 +2187,18 @@
         <v>镁合金 (Magnesium) HAGANE 机身</v>
       </c>
       <c r="P29" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Magnesium</v>
       </c>
       <c r="Q29" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="R29" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S29" t="str">
         <v>Reject candidate 'Hagane body system' because it is a technology/system term, not the actual material wording.</v>
       </c>
-      <c r="R29" t="str">
+      <c r="T29" t="str">
         <v>Candidate is a technology/system phrase instead of a specific body material.</v>
       </c>
     </row>
@@ -2075,12 +2249,18 @@
         <v>镁合金 (Magnesium) HAGANE 机身</v>
       </c>
       <c r="P30" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Magnesium</v>
       </c>
       <c r="Q30" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="R30" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S30" t="str">
         <v>Reject candidate 'Hagane body system' because it is a technology/system term, not the actual material wording.</v>
       </c>
-      <c r="R30" t="str">
+      <c r="T30" t="str">
         <v>Candidate is a technology/system phrase instead of a specific body material.</v>
       </c>
     </row>
@@ -2131,18 +2311,24 @@
         <v>镁合金 (Magnesium) HAGANE 机身</v>
       </c>
       <c r="P31" t="str">
-        <v>user_review_2026-04-16</v>
+        <v>Magnesium</v>
       </c>
       <c r="Q31" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="R31" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="S31" t="str">
         <v>Reject candidate 'Hagane body system' because it is a technology/system term, not the actual material wording.</v>
       </c>
-      <c r="R31" t="str">
+      <c r="T31" t="str">
         <v>Candidate is a technology/system phrase instead of a specific body material.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T31"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/GearSage-client/pkgGear/data_raw/experiment_reports/review/2026-04-16_shimano_baitcasting_reel_whitelist_review_filled.xlsx
+++ b/GearSage-client/pkgGear/data_raw/experiment_reports/review/2026-04-16_shimano_baitcasting_reel_whitelist_review_filled.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T31"/>
+  <dimension ref="A1:V31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,48 +421,54 @@
         <v>model_year</v>
       </c>
       <c r="F1" t="str">
+        <v>alias</v>
+      </c>
+      <c r="G1" t="str">
+        <v>version_signature</v>
+      </c>
+      <c r="H1" t="str">
         <v>sku</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>candidate_value</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>source_site</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>source_url</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>evidence_text</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>current_value_before_enrichment</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>year_scope_note</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>fitment_note</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>review_status</v>
       </c>
-      <c r="O1" t="str">
+      <c r="Q1" t="str">
         <v>approved_value_raw</v>
       </c>
-      <c r="P1" t="str">
+      <c r="R1" t="str">
         <v>approved_value</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="S1" t="str">
         <v>body_material_tech</v>
       </c>
-      <c r="R1" t="str">
+      <c r="T1" t="str">
         <v>reviewer</v>
       </c>
-      <c r="S1" t="str">
+      <c r="U1" t="str">
         <v>review_note</v>
       </c>
-      <c r="T1" t="str">
+      <c r="V1" t="str">
         <v>rejected_candidate_reason</v>
       </c>
     </row>
@@ -483,48 +489,54 @@
         <v>2021</v>
       </c>
       <c r="F2" t="str">
+        <v>21 Antares DC Japan model 2021- - Shimano - Casting Reels</v>
+      </c>
+      <c r="G2" t="str">
+        <v>ANTARES DC | 2021 | 6 sku variants</v>
+      </c>
+      <c r="H2" t="str">
         <v>ANTARES DC R</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="H2" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K2" t="str">
         <v>https://www.japantackle.com/casting-reels/shimano/shimano-21antaresdc.html</v>
       </c>
-      <c r="J2" t="str">
+      <c r="L2" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
-      <c r="L2" t="str">
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="M2" t="str">
+      <c r="O2" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="N2" t="str">
+      <c r="P2" t="str">
         <v>approved</v>
       </c>
-      <c r="O2" t="str">
+      <c r="Q2" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="P2" t="str">
+      <c r="R2" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="S2" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="R2" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
-      <c r="S2" t="str">
+      <c r="T2" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U2" t="str">
         <v>Correct and acceptable, but this appears to describe the 2021 ANTARES DC generation.</v>
       </c>
-      <c r="T2" t="str">
+      <c r="V2" t="str">
         <v/>
       </c>
     </row>
@@ -545,48 +557,54 @@
         <v>2021</v>
       </c>
       <c r="F3" t="str">
+        <v>21 Antares DC Japan model 2021- - Shimano - Casting Reels</v>
+      </c>
+      <c r="G3" t="str">
+        <v>ANTARES DC | 2021 | 6 sku variants</v>
+      </c>
+      <c r="H3" t="str">
         <v>ANTARES DC L</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="H3" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I3" t="str">
+      <c r="J3" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K3" t="str">
         <v>https://www.japantackle.com/casting-reels/shimano/shimano-21antaresdc.html</v>
       </c>
-      <c r="J3" t="str">
+      <c r="L3" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="M3" t="str">
+      <c r="O3" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="N3" t="str">
+      <c r="P3" t="str">
         <v>approved</v>
       </c>
-      <c r="O3" t="str">
+      <c r="Q3" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="P3" t="str">
+      <c r="R3" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="S3" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="R3" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
-      <c r="S3" t="str">
+      <c r="T3" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U3" t="str">
         <v>Correct and acceptable, but this appears to describe the 2021 ANTARES DC generation.</v>
       </c>
-      <c r="T3" t="str">
+      <c r="V3" t="str">
         <v/>
       </c>
     </row>
@@ -607,48 +625,54 @@
         <v>2021</v>
       </c>
       <c r="F4" t="str">
+        <v>21 Antares DC Japan model 2021- - Shimano - Casting Reels</v>
+      </c>
+      <c r="G4" t="str">
+        <v>ANTARES DC | 2021 | 6 sku variants</v>
+      </c>
+      <c r="H4" t="str">
         <v>ANTARES DC HG R</v>
       </c>
-      <c r="G4" t="str">
+      <c r="I4" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="H4" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I4" t="str">
+      <c r="J4" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K4" t="str">
         <v>https://www.japantackle.com/casting-reels/shimano/shimano-21antaresdc.html</v>
       </c>
-      <c r="J4" t="str">
+      <c r="L4" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="M4" t="str">
+      <c r="O4" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="N4" t="str">
+      <c r="P4" t="str">
         <v>approved</v>
       </c>
-      <c r="O4" t="str">
+      <c r="Q4" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="P4" t="str">
+      <c r="R4" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="Q4" t="str">
+      <c r="S4" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="R4" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
-      <c r="S4" t="str">
+      <c r="T4" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U4" t="str">
         <v>Correct and acceptable, but this appears to describe the 2021 ANTARES DC generation.</v>
       </c>
-      <c r="T4" t="str">
+      <c r="V4" t="str">
         <v/>
       </c>
     </row>
@@ -669,48 +693,54 @@
         <v>2021</v>
       </c>
       <c r="F5" t="str">
+        <v>21 Antares DC Japan model 2021- - Shimano - Casting Reels</v>
+      </c>
+      <c r="G5" t="str">
+        <v>ANTARES DC | 2021 | 6 sku variants</v>
+      </c>
+      <c r="H5" t="str">
         <v>ANTARES DC HG L</v>
       </c>
-      <c r="G5" t="str">
+      <c r="I5" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="H5" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I5" t="str">
+      <c r="J5" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K5" t="str">
         <v>https://www.japantackle.com/casting-reels/shimano/shimano-21antaresdc.html</v>
       </c>
-      <c r="J5" t="str">
+      <c r="L5" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="M5" t="str">
+      <c r="O5" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="N5" t="str">
+      <c r="P5" t="str">
         <v>approved</v>
       </c>
-      <c r="O5" t="str">
+      <c r="Q5" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="P5" t="str">
+      <c r="R5" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="Q5" t="str">
+      <c r="S5" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="R5" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
-      <c r="S5" t="str">
+      <c r="T5" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U5" t="str">
         <v>Correct and acceptable, but this appears to describe the 2021 ANTARES DC generation.</v>
       </c>
-      <c r="T5" t="str">
+      <c r="V5" t="str">
         <v/>
       </c>
     </row>
@@ -731,48 +761,54 @@
         <v>2021</v>
       </c>
       <c r="F6" t="str">
+        <v>21 Antares DC Japan model 2021- - Shimano - Casting Reels</v>
+      </c>
+      <c r="G6" t="str">
+        <v>ANTARES DC | 2021 | 6 sku variants</v>
+      </c>
+      <c r="H6" t="str">
         <v>ANTARES DC XG R</v>
       </c>
-      <c r="G6" t="str">
+      <c r="I6" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="H6" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I6" t="str">
+      <c r="J6" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K6" t="str">
         <v>https://www.japantackle.com/casting-reels/shimano/shimano-21antaresdc.html</v>
       </c>
-      <c r="J6" t="str">
+      <c r="L6" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="M6" t="str">
+      <c r="O6" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="N6" t="str">
+      <c r="P6" t="str">
         <v>approved</v>
       </c>
-      <c r="O6" t="str">
+      <c r="Q6" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="P6" t="str">
+      <c r="R6" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="Q6" t="str">
+      <c r="S6" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="R6" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
-      <c r="S6" t="str">
+      <c r="T6" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U6" t="str">
         <v>Correct and acceptable, but this appears to describe the 2021 ANTARES DC generation.</v>
       </c>
-      <c r="T6" t="str">
+      <c r="V6" t="str">
         <v/>
       </c>
     </row>
@@ -793,48 +829,54 @@
         <v>2021</v>
       </c>
       <c r="F7" t="str">
+        <v>21 Antares DC Japan model 2021- - Shimano - Casting Reels</v>
+      </c>
+      <c r="G7" t="str">
+        <v>ANTARES DC | 2021 | 6 sku variants</v>
+      </c>
+      <c r="H7" t="str">
         <v>ANTARES DC XG L</v>
       </c>
-      <c r="G7" t="str">
+      <c r="I7" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="H7" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I7" t="str">
+      <c r="J7" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K7" t="str">
         <v>https://www.japantackle.com/casting-reels/shimano/shimano-21antaresdc.html</v>
       </c>
-      <c r="J7" t="str">
+      <c r="L7" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="M7" t="str">
+      <c r="O7" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="N7" t="str">
+      <c r="P7" t="str">
         <v>approved</v>
       </c>
-      <c r="O7" t="str">
+      <c r="Q7" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="P7" t="str">
+      <c r="R7" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="Q7" t="str">
+      <c r="S7" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="R7" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
-      <c r="S7" t="str">
+      <c r="T7" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U7" t="str">
         <v>Correct and acceptable, but this appears to describe the 2021 ANTARES DC generation.</v>
       </c>
-      <c r="T7" t="str">
+      <c r="V7" t="str">
         <v/>
       </c>
     </row>
@@ -855,48 +897,54 @@
         <v>2023</v>
       </c>
       <c r="F8" t="str">
+        <v>23 Antares DC MD Monster Drive 2023- - Casting Reels</v>
+      </c>
+      <c r="G8" t="str">
+        <v>ANTARES DC MD | 2023 | 4 sku variants</v>
+      </c>
+      <c r="H8" t="str">
         <v>ANTARES DC MD HG RIGHT</v>
       </c>
-      <c r="G8" t="str">
+      <c r="I8" t="str">
         <v>metal frames</v>
       </c>
-      <c r="H8" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I8" t="str">
+      <c r="J8" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K8" t="str">
         <v>https://japantackle.com/casting-reels/shimano-23antares-dcmd.html</v>
       </c>
-      <c r="J8" t="str">
+      <c r="L8" t="str">
         <v>To maximize the chance to catch them, Antares DC MD has sturdy metal frames, enlarged 38mm dia, 21mm width spools, 20lb(JP)-100m line capacity, and fast gear ratios. MD tuned DC brake system is more finely tuned to draw the best performance from Magnum Light 3 spools to cast bulky large baits in comforts. Another ball bearing is added to main shaft support to remove plays and to improve cranking power.</v>
       </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
         <v>Bind to 2023 ANTARES DC MD. Same-series body material may differ across other years.</v>
       </c>
-      <c r="M8" t="str">
+      <c r="O8" t="str">
         <v>Manual override based on review knowledge: 2023 ANTARES DC MD body material is Magnesium.</v>
       </c>
-      <c r="N8" t="str">
+      <c r="P8" t="str">
         <v>approved_manual_override</v>
       </c>
-      <c r="O8" t="str">
+      <c r="Q8" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="P8" t="str">
+      <c r="R8" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="Q8" t="str">
-        <v/>
-      </c>
-      <c r="R8" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
       <c r="S8" t="str">
+        <v/>
+      </c>
+      <c r="T8" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U8" t="str">
         <v>Reject candidate 'metal frames' because it is not a specific material.</v>
       </c>
-      <c r="T8" t="str">
+      <c r="V8" t="str">
         <v>Candidate is generic wording, not an explicit material field.</v>
       </c>
     </row>
@@ -917,48 +965,54 @@
         <v>2023</v>
       </c>
       <c r="F9" t="str">
+        <v>23 Antares DC MD Monster Drive 2023- - Casting Reels</v>
+      </c>
+      <c r="G9" t="str">
+        <v>ANTARES DC MD | 2023 | 4 sku variants</v>
+      </c>
+      <c r="H9" t="str">
         <v>ANTARES DC MD HG LEFT</v>
       </c>
-      <c r="G9" t="str">
+      <c r="I9" t="str">
         <v>metal frames</v>
       </c>
-      <c r="H9" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I9" t="str">
+      <c r="J9" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K9" t="str">
         <v>https://japantackle.com/casting-reels/shimano-23antares-dcmd.html</v>
       </c>
-      <c r="J9" t="str">
+      <c r="L9" t="str">
         <v>To maximize the chance to catch them, Antares DC MD has sturdy metal frames, enlarged 38mm dia, 21mm width spools, 20lb(JP)-100m line capacity, and fast gear ratios. MD tuned DC brake system is more finely tuned to draw the best performance from Magnum Light 3 spools to cast bulky large baits in comforts. Another ball bearing is added to main shaft support to remove plays and to improve cranking power.</v>
       </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
         <v>Bind to 2023 ANTARES DC MD. Same-series body material may differ across other years.</v>
       </c>
-      <c r="M9" t="str">
+      <c r="O9" t="str">
         <v>Manual override based on review knowledge: 2023 ANTARES DC MD body material is Magnesium.</v>
       </c>
-      <c r="N9" t="str">
+      <c r="P9" t="str">
         <v>approved_manual_override</v>
       </c>
-      <c r="O9" t="str">
+      <c r="Q9" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="P9" t="str">
+      <c r="R9" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="Q9" t="str">
-        <v/>
-      </c>
-      <c r="R9" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
       <c r="S9" t="str">
+        <v/>
+      </c>
+      <c r="T9" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U9" t="str">
         <v>Reject candidate 'metal frames' because it is not a specific material.</v>
       </c>
-      <c r="T9" t="str">
+      <c r="V9" t="str">
         <v>Candidate is generic wording, not an explicit material field.</v>
       </c>
     </row>
@@ -979,48 +1033,54 @@
         <v>2023</v>
       </c>
       <c r="F10" t="str">
+        <v>23 Antares DC MD Monster Drive 2023- - Casting Reels</v>
+      </c>
+      <c r="G10" t="str">
+        <v>ANTARES DC MD | 2023 | 4 sku variants</v>
+      </c>
+      <c r="H10" t="str">
         <v>ANTARES DC MD XG RIGHT</v>
       </c>
-      <c r="G10" t="str">
+      <c r="I10" t="str">
         <v>metal frames</v>
       </c>
-      <c r="H10" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I10" t="str">
+      <c r="J10" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K10" t="str">
         <v>https://japantackle.com/casting-reels/shimano-23antares-dcmd.html</v>
       </c>
-      <c r="J10" t="str">
+      <c r="L10" t="str">
         <v>To maximize the chance to catch them, Antares DC MD has sturdy metal frames, enlarged 38mm dia, 21mm width spools, 20lb(JP)-100m line capacity, and fast gear ratios. MD tuned DC brake system is more finely tuned to draw the best performance from Magnum Light 3 spools to cast bulky large baits in comforts. Another ball bearing is added to main shaft support to remove plays and to improve cranking power.</v>
       </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
         <v>Bind to 2023 ANTARES DC MD. Same-series body material may differ across other years.</v>
       </c>
-      <c r="M10" t="str">
+      <c r="O10" t="str">
         <v>Manual override based on review knowledge: 2023 ANTARES DC MD body material is Magnesium.</v>
       </c>
-      <c r="N10" t="str">
+      <c r="P10" t="str">
         <v>approved_manual_override</v>
       </c>
-      <c r="O10" t="str">
+      <c r="Q10" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="P10" t="str">
+      <c r="R10" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="Q10" t="str">
-        <v/>
-      </c>
-      <c r="R10" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
       <c r="S10" t="str">
+        <v/>
+      </c>
+      <c r="T10" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U10" t="str">
         <v>Reject candidate 'metal frames' because it is not a specific material.</v>
       </c>
-      <c r="T10" t="str">
+      <c r="V10" t="str">
         <v>Candidate is generic wording, not an explicit material field.</v>
       </c>
     </row>
@@ -1041,48 +1101,54 @@
         <v>2023</v>
       </c>
       <c r="F11" t="str">
+        <v>23 Antares DC MD Monster Drive 2023- - Casting Reels</v>
+      </c>
+      <c r="G11" t="str">
+        <v>ANTARES DC MD | 2023 | 4 sku variants</v>
+      </c>
+      <c r="H11" t="str">
         <v>ANTARES DC MD XG LEFT</v>
       </c>
-      <c r="G11" t="str">
+      <c r="I11" t="str">
         <v>metal frames</v>
       </c>
-      <c r="H11" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I11" t="str">
+      <c r="J11" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K11" t="str">
         <v>https://japantackle.com/casting-reels/shimano-23antares-dcmd.html</v>
       </c>
-      <c r="J11" t="str">
+      <c r="L11" t="str">
         <v>To maximize the chance to catch them, Antares DC MD has sturdy metal frames, enlarged 38mm dia, 21mm width spools, 20lb(JP)-100m line capacity, and fast gear ratios. MD tuned DC brake system is more finely tuned to draw the best performance from Magnum Light 3 spools to cast bulky large baits in comforts. Another ball bearing is added to main shaft support to remove plays and to improve cranking power.</v>
       </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
         <v>Bind to 2023 ANTARES DC MD. Same-series body material may differ across other years.</v>
       </c>
-      <c r="M11" t="str">
+      <c r="O11" t="str">
         <v>Manual override based on review knowledge: 2023 ANTARES DC MD body material is Magnesium.</v>
       </c>
-      <c r="N11" t="str">
+      <c r="P11" t="str">
         <v>approved_manual_override</v>
       </c>
-      <c r="O11" t="str">
+      <c r="Q11" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="P11" t="str">
+      <c r="R11" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="Q11" t="str">
-        <v/>
-      </c>
-      <c r="R11" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
       <c r="S11" t="str">
+        <v/>
+      </c>
+      <c r="T11" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U11" t="str">
         <v>Reject candidate 'metal frames' because it is not a specific material.</v>
       </c>
-      <c r="T11" t="str">
+      <c r="V11" t="str">
         <v>Candidate is generic wording, not an explicit material field.</v>
       </c>
     </row>
@@ -1103,48 +1169,54 @@
         <v>2024</v>
       </c>
       <c r="F12" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="H12" t="str">
         <v>Metanium DC 70</v>
       </c>
-      <c r="G12" t="str">
+      <c r="I12" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="H12" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I12" t="str">
+      <c r="J12" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K12" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="J12" t="str">
+      <c r="L12" t="str">
         <v>All New Shimano 2024 Metanium DC is the versatile bait caster for all around use. Core solid metal body holds every components solid. The state of arts i-DC5 brake system casts very smooth for long, and the new material dial is changeable without opening the side plate. MGL 3 spool offers fast spool acceleration.</v>
       </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="M12" t="str">
+      <c r="O12" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
-      <c r="N12" t="str">
+      <c r="P12" t="str">
         <v>approved_manual_override</v>
       </c>
-      <c r="O12" t="str">
+      <c r="Q12" t="str">
         <v>CORESOLID BODY 镁合金一体成型</v>
       </c>
-      <c r="P12" t="str">
+      <c r="R12" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="Q12" t="str">
+      <c r="S12" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
-      <c r="R12" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
-      <c r="S12" t="str">
+      <c r="T12" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U12" t="str">
         <v>Reject candidate 'Core solid metal body' because it is a technology phrase, not a precise material expression.</v>
       </c>
-      <c r="T12" t="str">
+      <c r="V12" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
     </row>
@@ -1165,48 +1237,54 @@
         <v>2024</v>
       </c>
       <c r="F13" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="H13" t="str">
         <v>Metanium DC 70</v>
       </c>
-      <c r="G13" t="str">
+      <c r="I13" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="H13" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I13" t="str">
+      <c r="J13" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K13" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="J13" t="str">
+      <c r="L13" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="M13" t="str">
+      <c r="O13" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="N13" t="str">
+      <c r="P13" t="str">
         <v>approved</v>
       </c>
-      <c r="O13" t="str">
+      <c r="Q13" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="P13" t="str">
+      <c r="R13" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="Q13" t="str">
-        <v/>
-      </c>
-      <c r="R13" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
       <c r="S13" t="str">
+        <v/>
+      </c>
+      <c r="T13" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U13" t="str">
         <v>Correct and acceptable, but keep year awareness for other Metanium DC generations.</v>
       </c>
-      <c r="T13" t="str">
+      <c r="V13" t="str">
         <v/>
       </c>
     </row>
@@ -1227,48 +1305,54 @@
         <v>2024</v>
       </c>
       <c r="F14" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="H14" t="str">
         <v>Metanium DC 71</v>
       </c>
-      <c r="G14" t="str">
+      <c r="I14" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="H14" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I14" t="str">
+      <c r="J14" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K14" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="J14" t="str">
+      <c r="L14" t="str">
         <v>All New Shimano 2024 Metanium DC is the versatile bait caster for all around use. Core solid metal body holds every components solid. The state of arts i-DC5 brake system casts very smooth for long, and the new material dial is changeable without opening the side plate. MGL 3 spool offers fast spool acceleration.</v>
       </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="M14" t="str">
+      <c r="O14" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
-      <c r="N14" t="str">
+      <c r="P14" t="str">
         <v>approved_manual_override</v>
       </c>
-      <c r="O14" t="str">
+      <c r="Q14" t="str">
         <v>CORESOLID BODY 镁合金一体成型</v>
       </c>
-      <c r="P14" t="str">
+      <c r="R14" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="Q14" t="str">
+      <c r="S14" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
-      <c r="R14" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
-      <c r="S14" t="str">
+      <c r="T14" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U14" t="str">
         <v>Reject candidate 'Core solid metal body' because it is a technology phrase, not a precise material expression.</v>
       </c>
-      <c r="T14" t="str">
+      <c r="V14" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
     </row>
@@ -1289,48 +1373,54 @@
         <v>2024</v>
       </c>
       <c r="F15" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="H15" t="str">
         <v>Metanium DC 71</v>
       </c>
-      <c r="G15" t="str">
+      <c r="I15" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="H15" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I15" t="str">
+      <c r="J15" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K15" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="J15" t="str">
+      <c r="L15" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="M15" t="str">
+      <c r="O15" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="N15" t="str">
+      <c r="P15" t="str">
         <v>approved</v>
       </c>
-      <c r="O15" t="str">
+      <c r="Q15" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="P15" t="str">
+      <c r="R15" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="Q15" t="str">
-        <v/>
-      </c>
-      <c r="R15" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
       <c r="S15" t="str">
+        <v/>
+      </c>
+      <c r="T15" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U15" t="str">
         <v>Correct and acceptable, but keep year awareness for other Metanium DC generations.</v>
       </c>
-      <c r="T15" t="str">
+      <c r="V15" t="str">
         <v/>
       </c>
     </row>
@@ -1351,48 +1441,54 @@
         <v>2024</v>
       </c>
       <c r="F16" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="H16" t="str">
         <v>Metanium DC 70HG</v>
       </c>
-      <c r="G16" t="str">
+      <c r="I16" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="H16" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I16" t="str">
+      <c r="J16" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K16" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="J16" t="str">
+      <c r="L16" t="str">
         <v>All New Shimano 2024 Metanium DC is the versatile bait caster for all around use. Core solid metal body holds every components solid. The state of arts i-DC5 brake system casts very smooth for long, and the new material dial is changeable without opening the side plate. MGL 3 spool offers fast spool acceleration.</v>
       </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-      <c r="L16" t="str">
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="M16" t="str">
+      <c r="O16" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
-      <c r="N16" t="str">
+      <c r="P16" t="str">
         <v>approved_manual_override</v>
       </c>
-      <c r="O16" t="str">
+      <c r="Q16" t="str">
         <v>CORESOLID BODY 镁合金一体成型</v>
       </c>
-      <c r="P16" t="str">
+      <c r="R16" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="Q16" t="str">
+      <c r="S16" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
-      <c r="R16" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
-      <c r="S16" t="str">
+      <c r="T16" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U16" t="str">
         <v>Reject candidate 'Core solid metal body' because it is a technology phrase, not a precise material expression.</v>
       </c>
-      <c r="T16" t="str">
+      <c r="V16" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
     </row>
@@ -1413,48 +1509,54 @@
         <v>2024</v>
       </c>
       <c r="F17" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="H17" t="str">
         <v>Metanium DC 70HG</v>
       </c>
-      <c r="G17" t="str">
+      <c r="I17" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="H17" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I17" t="str">
+      <c r="J17" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K17" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="J17" t="str">
+      <c r="L17" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="K17" t="str">
-        <v/>
-      </c>
-      <c r="L17" t="str">
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="M17" t="str">
+      <c r="O17" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="N17" t="str">
+      <c r="P17" t="str">
         <v>approved</v>
       </c>
-      <c r="O17" t="str">
+      <c r="Q17" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="P17" t="str">
+      <c r="R17" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="Q17" t="str">
-        <v/>
-      </c>
-      <c r="R17" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
       <c r="S17" t="str">
+        <v/>
+      </c>
+      <c r="T17" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U17" t="str">
         <v>Correct and acceptable, but keep year awareness for other Metanium DC generations.</v>
       </c>
-      <c r="T17" t="str">
+      <c r="V17" t="str">
         <v/>
       </c>
     </row>
@@ -1475,48 +1577,54 @@
         <v>2024</v>
       </c>
       <c r="F18" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="H18" t="str">
         <v>Metanium DC 71HG</v>
       </c>
-      <c r="G18" t="str">
+      <c r="I18" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="H18" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I18" t="str">
+      <c r="J18" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K18" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="J18" t="str">
+      <c r="L18" t="str">
         <v>All New Shimano 2024 Metanium DC is the versatile bait caster for all around use. Core solid metal body holds every components solid. The state of arts i-DC5 brake system casts very smooth for long, and the new material dial is changeable without opening the side plate. MGL 3 spool offers fast spool acceleration.</v>
       </c>
-      <c r="K18" t="str">
-        <v/>
-      </c>
-      <c r="L18" t="str">
+      <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="M18" t="str">
+      <c r="O18" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
-      <c r="N18" t="str">
+      <c r="P18" t="str">
         <v>approved_manual_override</v>
       </c>
-      <c r="O18" t="str">
+      <c r="Q18" t="str">
         <v>CORESOLID BODY 镁合金一体成型</v>
       </c>
-      <c r="P18" t="str">
+      <c r="R18" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="Q18" t="str">
+      <c r="S18" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
-      <c r="R18" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
-      <c r="S18" t="str">
+      <c r="T18" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U18" t="str">
         <v>Reject candidate 'Core solid metal body' because it is a technology phrase, not a precise material expression.</v>
       </c>
-      <c r="T18" t="str">
+      <c r="V18" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
     </row>
@@ -1537,48 +1645,54 @@
         <v>2024</v>
       </c>
       <c r="F19" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="H19" t="str">
         <v>Metanium DC 71HG</v>
       </c>
-      <c r="G19" t="str">
+      <c r="I19" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="H19" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I19" t="str">
+      <c r="J19" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K19" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="J19" t="str">
+      <c r="L19" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="K19" t="str">
-        <v/>
-      </c>
-      <c r="L19" t="str">
+      <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="M19" t="str">
+      <c r="O19" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="N19" t="str">
+      <c r="P19" t="str">
         <v>approved</v>
       </c>
-      <c r="O19" t="str">
+      <c r="Q19" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="P19" t="str">
+      <c r="R19" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="Q19" t="str">
-        <v/>
-      </c>
-      <c r="R19" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
       <c r="S19" t="str">
+        <v/>
+      </c>
+      <c r="T19" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U19" t="str">
         <v>Correct and acceptable, but keep year awareness for other Metanium DC generations.</v>
       </c>
-      <c r="T19" t="str">
+      <c r="V19" t="str">
         <v/>
       </c>
     </row>
@@ -1599,48 +1713,54 @@
         <v>2024</v>
       </c>
       <c r="F20" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="H20" t="str">
         <v>Metanium DC 70XG</v>
       </c>
-      <c r="G20" t="str">
+      <c r="I20" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="H20" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I20" t="str">
+      <c r="J20" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K20" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="J20" t="str">
+      <c r="L20" t="str">
         <v>All New Shimano 2024 Metanium DC is the versatile bait caster for all around use. Core solid metal body holds every components solid. The state of arts i-DC5 brake system casts very smooth for long, and the new material dial is changeable without opening the side plate. MGL 3 spool offers fast spool acceleration.</v>
       </c>
-      <c r="K20" t="str">
-        <v/>
-      </c>
-      <c r="L20" t="str">
+      <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="M20" t="str">
+      <c r="O20" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
-      <c r="N20" t="str">
+      <c r="P20" t="str">
         <v>approved_manual_override</v>
       </c>
-      <c r="O20" t="str">
+      <c r="Q20" t="str">
         <v>CORESOLID BODY 镁合金一体成型</v>
       </c>
-      <c r="P20" t="str">
+      <c r="R20" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="Q20" t="str">
+      <c r="S20" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
-      <c r="R20" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
-      <c r="S20" t="str">
+      <c r="T20" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U20" t="str">
         <v>Reject candidate 'Core solid metal body' because it is a technology phrase, not a precise material expression.</v>
       </c>
-      <c r="T20" t="str">
+      <c r="V20" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
     </row>
@@ -1661,48 +1781,54 @@
         <v>2024</v>
       </c>
       <c r="F21" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="H21" t="str">
         <v>Metanium DC 70XG</v>
       </c>
-      <c r="G21" t="str">
+      <c r="I21" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="H21" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I21" t="str">
+      <c r="J21" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K21" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="J21" t="str">
+      <c r="L21" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="K21" t="str">
-        <v/>
-      </c>
-      <c r="L21" t="str">
+      <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="M21" t="str">
+      <c r="O21" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="N21" t="str">
+      <c r="P21" t="str">
         <v>approved</v>
       </c>
-      <c r="O21" t="str">
+      <c r="Q21" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="P21" t="str">
+      <c r="R21" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="Q21" t="str">
-        <v/>
-      </c>
-      <c r="R21" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
       <c r="S21" t="str">
+        <v/>
+      </c>
+      <c r="T21" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U21" t="str">
         <v>Correct and acceptable, but keep year awareness for other Metanium DC generations.</v>
       </c>
-      <c r="T21" t="str">
+      <c r="V21" t="str">
         <v/>
       </c>
     </row>
@@ -1723,48 +1849,54 @@
         <v>2024</v>
       </c>
       <c r="F22" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="H22" t="str">
         <v>Metanium DC 71XG</v>
       </c>
-      <c r="G22" t="str">
+      <c r="I22" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="H22" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I22" t="str">
+      <c r="J22" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K22" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="J22" t="str">
+      <c r="L22" t="str">
         <v>All New Shimano 2024 Metanium DC is the versatile bait caster for all around use. Core solid metal body holds every components solid. The state of arts i-DC5 brake system casts very smooth for long, and the new material dial is changeable without opening the side plate. MGL 3 spool offers fast spool acceleration.</v>
       </c>
-      <c r="K22" t="str">
-        <v/>
-      </c>
-      <c r="L22" t="str">
+      <c r="M22" t="str">
+        <v/>
+      </c>
+      <c r="N22" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="M22" t="str">
+      <c r="O22" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
-      <c r="N22" t="str">
+      <c r="P22" t="str">
         <v>approved_manual_override</v>
       </c>
-      <c r="O22" t="str">
+      <c r="Q22" t="str">
         <v>CORESOLID BODY 镁合金一体成型</v>
       </c>
-      <c r="P22" t="str">
+      <c r="R22" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="Q22" t="str">
+      <c r="S22" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
-      <c r="R22" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
-      <c r="S22" t="str">
+      <c r="T22" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U22" t="str">
         <v>Reject candidate 'Core solid metal body' because it is a technology phrase, not a precise material expression.</v>
       </c>
-      <c r="T22" t="str">
+      <c r="V22" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
     </row>
@@ -1785,48 +1917,54 @@
         <v>2024</v>
       </c>
       <c r="F23" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="H23" t="str">
         <v>Metanium DC 71XG</v>
       </c>
-      <c r="G23" t="str">
+      <c r="I23" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="H23" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I23" t="str">
+      <c r="J23" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K23" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="J23" t="str">
+      <c r="L23" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="K23" t="str">
-        <v/>
-      </c>
-      <c r="L23" t="str">
+      <c r="M23" t="str">
+        <v/>
+      </c>
+      <c r="N23" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="M23" t="str">
+      <c r="O23" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="N23" t="str">
+      <c r="P23" t="str">
         <v>approved</v>
       </c>
-      <c r="O23" t="str">
+      <c r="Q23" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="P23" t="str">
+      <c r="R23" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="Q23" t="str">
-        <v/>
-      </c>
-      <c r="R23" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
       <c r="S23" t="str">
+        <v/>
+      </c>
+      <c r="T23" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U23" t="str">
         <v>Correct and acceptable, but keep year awareness for other Metanium DC generations.</v>
       </c>
-      <c r="T23" t="str">
+      <c r="V23" t="str">
         <v/>
       </c>
     </row>
@@ -1844,51 +1982,57 @@
         <v>CALCUTTA CONQUEST BFS</v>
       </c>
       <c r="E24" t="str">
-        <v/>
+        <v>2026</v>
       </c>
       <c r="F24" t="str">
+        <v>23 Calcutta Conquest BFS Japan model 2023- - Shimano - Casting Reels</v>
+      </c>
+      <c r="G24" t="str">
+        <v>CALCUTTA CONQUEST BFS | 2026 | 4 sku variants</v>
+      </c>
+      <c r="H24" t="str">
         <v>CALCUTTA CONQUEST BFS HG RIGHT</v>
       </c>
-      <c r="G24" t="str">
+      <c r="I24" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="H24" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I24" t="str">
+      <c r="J24" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K24" t="str">
         <v>https://japantackle.com/casting-reels/shimano/reg0000334.html</v>
       </c>
-      <c r="J24" t="str">
+      <c r="L24" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="K24" t="str">
-        <v/>
-      </c>
-      <c r="L24" t="str">
+      <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
         <v>Do not spread by model-only match. Keep reel_id and SKU binding until year/version is confirmed.</v>
       </c>
-      <c r="M24" t="str">
+      <c r="O24" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="N24" t="str">
+      <c r="P24" t="str">
         <v>approved</v>
       </c>
-      <c r="O24" t="str">
+      <c r="Q24" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="P24" t="str">
+      <c r="R24" t="str">
         <v>Aluminum</v>
       </c>
-      <c r="Q24" t="str">
+      <c r="S24" t="str">
         <v>全加工</v>
       </c>
-      <c r="R24" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
-      <c r="S24" t="str">
+      <c r="T24" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U24" t="str">
         <v>Correct and acceptable, but keep year awareness for future generations.</v>
       </c>
-      <c r="T24" t="str">
+      <c r="V24" t="str">
         <v/>
       </c>
     </row>
@@ -1906,51 +2050,57 @@
         <v>CALCUTTA CONQUEST BFS</v>
       </c>
       <c r="E25" t="str">
-        <v/>
+        <v>2026</v>
       </c>
       <c r="F25" t="str">
+        <v>23 Calcutta Conquest BFS Japan model 2023- - Shimano - Casting Reels</v>
+      </c>
+      <c r="G25" t="str">
+        <v>CALCUTTA CONQUEST BFS | 2026 | 4 sku variants</v>
+      </c>
+      <c r="H25" t="str">
         <v>CALCUTTA CONQUEST BFS HG LEFT</v>
       </c>
-      <c r="G25" t="str">
+      <c r="I25" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="H25" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I25" t="str">
+      <c r="J25" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K25" t="str">
         <v>https://japantackle.com/casting-reels/shimano/reg0000334.html</v>
       </c>
-      <c r="J25" t="str">
+      <c r="L25" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="K25" t="str">
-        <v/>
-      </c>
-      <c r="L25" t="str">
+      <c r="M25" t="str">
+        <v/>
+      </c>
+      <c r="N25" t="str">
         <v>Do not spread by model-only match. Keep reel_id and SKU binding until year/version is confirmed.</v>
       </c>
-      <c r="M25" t="str">
+      <c r="O25" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="N25" t="str">
+      <c r="P25" t="str">
         <v>approved</v>
       </c>
-      <c r="O25" t="str">
+      <c r="Q25" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="P25" t="str">
+      <c r="R25" t="str">
         <v>Aluminum</v>
       </c>
-      <c r="Q25" t="str">
+      <c r="S25" t="str">
         <v>全加工</v>
       </c>
-      <c r="R25" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
-      <c r="S25" t="str">
+      <c r="T25" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U25" t="str">
         <v>Correct and acceptable, but keep year awareness for future generations.</v>
       </c>
-      <c r="T25" t="str">
+      <c r="V25" t="str">
         <v/>
       </c>
     </row>
@@ -1968,51 +2118,57 @@
         <v>CALCUTTA CONQUEST BFS</v>
       </c>
       <c r="E26" t="str">
-        <v/>
+        <v>2026</v>
       </c>
       <c r="F26" t="str">
+        <v>23 Calcutta Conquest BFS Japan model 2023- - Shimano - Casting Reels</v>
+      </c>
+      <c r="G26" t="str">
+        <v>CALCUTTA CONQUEST BFS | 2026 | 4 sku variants</v>
+      </c>
+      <c r="H26" t="str">
         <v>CALCUTTA CONQUEST BFS XG RIGHT</v>
       </c>
-      <c r="G26" t="str">
+      <c r="I26" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="H26" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I26" t="str">
+      <c r="J26" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K26" t="str">
         <v>https://japantackle.com/casting-reels/shimano/reg0000334.html</v>
       </c>
-      <c r="J26" t="str">
+      <c r="L26" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="K26" t="str">
-        <v/>
-      </c>
-      <c r="L26" t="str">
+      <c r="M26" t="str">
+        <v/>
+      </c>
+      <c r="N26" t="str">
         <v>Do not spread by model-only match. Keep reel_id and SKU binding until year/version is confirmed.</v>
       </c>
-      <c r="M26" t="str">
+      <c r="O26" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="N26" t="str">
+      <c r="P26" t="str">
         <v>approved</v>
       </c>
-      <c r="O26" t="str">
+      <c r="Q26" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="P26" t="str">
+      <c r="R26" t="str">
         <v>Aluminum</v>
       </c>
-      <c r="Q26" t="str">
+      <c r="S26" t="str">
         <v>全加工</v>
       </c>
-      <c r="R26" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
-      <c r="S26" t="str">
+      <c r="T26" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U26" t="str">
         <v>Correct and acceptable, but keep year awareness for future generations.</v>
       </c>
-      <c r="T26" t="str">
+      <c r="V26" t="str">
         <v/>
       </c>
     </row>
@@ -2030,51 +2186,57 @@
         <v>CALCUTTA CONQUEST BFS</v>
       </c>
       <c r="E27" t="str">
-        <v/>
+        <v>2026</v>
       </c>
       <c r="F27" t="str">
+        <v>23 Calcutta Conquest BFS Japan model 2023- - Shimano - Casting Reels</v>
+      </c>
+      <c r="G27" t="str">
+        <v>CALCUTTA CONQUEST BFS | 2026 | 4 sku variants</v>
+      </c>
+      <c r="H27" t="str">
         <v>CALCUTTA CONQUEST BFS XG LEFT</v>
       </c>
-      <c r="G27" t="str">
+      <c r="I27" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="H27" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I27" t="str">
+      <c r="J27" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K27" t="str">
         <v>https://japantackle.com/casting-reels/shimano/reg0000334.html</v>
       </c>
-      <c r="J27" t="str">
+      <c r="L27" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="K27" t="str">
-        <v/>
-      </c>
-      <c r="L27" t="str">
+      <c r="M27" t="str">
+        <v/>
+      </c>
+      <c r="N27" t="str">
         <v>Do not spread by model-only match. Keep reel_id and SKU binding until year/version is confirmed.</v>
       </c>
-      <c r="M27" t="str">
+      <c r="O27" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="N27" t="str">
+      <c r="P27" t="str">
         <v>approved</v>
       </c>
-      <c r="O27" t="str">
+      <c r="Q27" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="P27" t="str">
+      <c r="R27" t="str">
         <v>Aluminum</v>
       </c>
-      <c r="Q27" t="str">
+      <c r="S27" t="str">
         <v>全加工</v>
       </c>
-      <c r="R27" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
-      <c r="S27" t="str">
+      <c r="T27" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U27" t="str">
         <v>Correct and acceptable, but keep year awareness for future generations.</v>
       </c>
-      <c r="T27" t="str">
+      <c r="V27" t="str">
         <v/>
       </c>
     </row>
@@ -2092,51 +2254,57 @@
         <v>ALDEBARAN BFS</v>
       </c>
       <c r="E28" t="str">
-        <v/>
+        <v>2026</v>
       </c>
       <c r="F28" t="str">
+        <v>22 Aldebaran BFS, ultimate finesse 2.0g, 2022- - 2026 Spring Trout Special</v>
+      </c>
+      <c r="G28" t="str">
+        <v>ALDEBARAN BFS | 2026 | 4 sku variants</v>
+      </c>
+      <c r="H28" t="str">
         <v>ALDEBARAN BFS HG R</v>
       </c>
-      <c r="G28" t="str">
+      <c r="I28" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="H28" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I28" t="str">
+      <c r="J28" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K28" t="str">
         <v>https://japantackle.com/special/reg0000317.html</v>
       </c>
-      <c r="J28" t="str">
+      <c r="L28" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="K28" t="str">
-        <v/>
-      </c>
-      <c r="L28" t="str">
+      <c r="M28" t="str">
+        <v/>
+      </c>
+      <c r="N28" t="str">
         <v>Aldebaran BFS body material must stay bound to reel_id and SKU until year/version is confirmed.</v>
       </c>
-      <c r="M28" t="str">
+      <c r="O28" t="str">
         <v>Manual override based on review knowledge: body wording should reflect Magnesium / HAGANE body, not 'Hagane body system'.</v>
       </c>
-      <c r="N28" t="str">
+      <c r="P28" t="str">
         <v>approved_manual_override</v>
       </c>
-      <c r="O28" t="str">
+      <c r="Q28" t="str">
         <v>镁合金 (Magnesium) HAGANE 机身</v>
       </c>
-      <c r="P28" t="str">
+      <c r="R28" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="Q28" t="str">
+      <c r="S28" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="R28" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
-      <c r="S28" t="str">
+      <c r="T28" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U28" t="str">
         <v>Reject candidate 'Hagane body system' because it is a technology/system term, not the actual material wording.</v>
       </c>
-      <c r="T28" t="str">
+      <c r="V28" t="str">
         <v>Candidate is a technology/system phrase instead of a specific body material.</v>
       </c>
     </row>
@@ -2154,51 +2322,57 @@
         <v>ALDEBARAN BFS</v>
       </c>
       <c r="E29" t="str">
-        <v/>
+        <v>2026</v>
       </c>
       <c r="F29" t="str">
+        <v>22 Aldebaran BFS, ultimate finesse 2.0g, 2022- - 2026 Spring Trout Special</v>
+      </c>
+      <c r="G29" t="str">
+        <v>ALDEBARAN BFS | 2026 | 4 sku variants</v>
+      </c>
+      <c r="H29" t="str">
         <v>ALDEBARAN BFS HG L</v>
       </c>
-      <c r="G29" t="str">
+      <c r="I29" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="H29" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I29" t="str">
+      <c r="J29" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K29" t="str">
         <v>https://japantackle.com/special/reg0000317.html</v>
       </c>
-      <c r="J29" t="str">
+      <c r="L29" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="K29" t="str">
-        <v/>
-      </c>
-      <c r="L29" t="str">
+      <c r="M29" t="str">
+        <v/>
+      </c>
+      <c r="N29" t="str">
         <v>Aldebaran BFS body material must stay bound to reel_id and SKU until year/version is confirmed.</v>
       </c>
-      <c r="M29" t="str">
+      <c r="O29" t="str">
         <v>Manual override based on review knowledge: body wording should reflect Magnesium / HAGANE body, not 'Hagane body system'.</v>
       </c>
-      <c r="N29" t="str">
+      <c r="P29" t="str">
         <v>approved_manual_override</v>
       </c>
-      <c r="O29" t="str">
+      <c r="Q29" t="str">
         <v>镁合金 (Magnesium) HAGANE 机身</v>
       </c>
-      <c r="P29" t="str">
+      <c r="R29" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="Q29" t="str">
+      <c r="S29" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="R29" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
-      <c r="S29" t="str">
+      <c r="T29" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U29" t="str">
         <v>Reject candidate 'Hagane body system' because it is a technology/system term, not the actual material wording.</v>
       </c>
-      <c r="T29" t="str">
+      <c r="V29" t="str">
         <v>Candidate is a technology/system phrase instead of a specific body material.</v>
       </c>
     </row>
@@ -2216,51 +2390,57 @@
         <v>ALDEBARAN BFS</v>
       </c>
       <c r="E30" t="str">
-        <v/>
+        <v>2026</v>
       </c>
       <c r="F30" t="str">
+        <v>22 Aldebaran BFS, ultimate finesse 2.0g, 2022- - 2026 Spring Trout Special</v>
+      </c>
+      <c r="G30" t="str">
+        <v>ALDEBARAN BFS | 2026 | 4 sku variants</v>
+      </c>
+      <c r="H30" t="str">
         <v>ALDEBARAN BFS XG R</v>
       </c>
-      <c r="G30" t="str">
+      <c r="I30" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="H30" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I30" t="str">
+      <c r="J30" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K30" t="str">
         <v>https://japantackle.com/special/reg0000317.html</v>
       </c>
-      <c r="J30" t="str">
+      <c r="L30" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="K30" t="str">
-        <v/>
-      </c>
-      <c r="L30" t="str">
+      <c r="M30" t="str">
+        <v/>
+      </c>
+      <c r="N30" t="str">
         <v>Aldebaran BFS body material must stay bound to reel_id and SKU until year/version is confirmed.</v>
       </c>
-      <c r="M30" t="str">
+      <c r="O30" t="str">
         <v>Manual override based on review knowledge: body wording should reflect Magnesium / HAGANE body, not 'Hagane body system'.</v>
       </c>
-      <c r="N30" t="str">
+      <c r="P30" t="str">
         <v>approved_manual_override</v>
       </c>
-      <c r="O30" t="str">
+      <c r="Q30" t="str">
         <v>镁合金 (Magnesium) HAGANE 机身</v>
       </c>
-      <c r="P30" t="str">
+      <c r="R30" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="Q30" t="str">
+      <c r="S30" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="R30" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
-      <c r="S30" t="str">
+      <c r="T30" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U30" t="str">
         <v>Reject candidate 'Hagane body system' because it is a technology/system term, not the actual material wording.</v>
       </c>
-      <c r="T30" t="str">
+      <c r="V30" t="str">
         <v>Candidate is a technology/system phrase instead of a specific body material.</v>
       </c>
     </row>
@@ -2278,57 +2458,63 @@
         <v>ALDEBARAN BFS</v>
       </c>
       <c r="E31" t="str">
-        <v/>
+        <v>2026</v>
       </c>
       <c r="F31" t="str">
+        <v>22 Aldebaran BFS, ultimate finesse 2.0g, 2022- - 2026 Spring Trout Special</v>
+      </c>
+      <c r="G31" t="str">
+        <v>ALDEBARAN BFS | 2026 | 4 sku variants</v>
+      </c>
+      <c r="H31" t="str">
         <v>ALDEBARAN BFS XG L</v>
       </c>
-      <c r="G31" t="str">
+      <c r="I31" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="H31" t="str">
-        <v>JapanTackle</v>
-      </c>
-      <c r="I31" t="str">
+      <c r="J31" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="K31" t="str">
         <v>https://japantackle.com/special/reg0000317.html</v>
       </c>
-      <c r="J31" t="str">
+      <c r="L31" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="K31" t="str">
-        <v/>
-      </c>
-      <c r="L31" t="str">
+      <c r="M31" t="str">
+        <v/>
+      </c>
+      <c r="N31" t="str">
         <v>Aldebaran BFS body material must stay bound to reel_id and SKU until year/version is confirmed.</v>
       </c>
-      <c r="M31" t="str">
+      <c r="O31" t="str">
         <v>Manual override based on review knowledge: body wording should reflect Magnesium / HAGANE body, not 'Hagane body system'.</v>
       </c>
-      <c r="N31" t="str">
+      <c r="P31" t="str">
         <v>approved_manual_override</v>
       </c>
-      <c r="O31" t="str">
+      <c r="Q31" t="str">
         <v>镁合金 (Magnesium) HAGANE 机身</v>
       </c>
-      <c r="P31" t="str">
+      <c r="R31" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="Q31" t="str">
+      <c r="S31" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="R31" t="str">
-        <v>user_review_2026-04-16</v>
-      </c>
-      <c r="S31" t="str">
+      <c r="T31" t="str">
+        <v>user_review_2026-04-16</v>
+      </c>
+      <c r="U31" t="str">
         <v>Reject candidate 'Hagane body system' because it is a technology/system term, not the actual material wording.</v>
       </c>
-      <c r="T31" t="str">
+      <c r="V31" t="str">
         <v>Candidate is a technology/system phrase instead of a specific body material.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:V31"/>
   </ignoredErrors>
 </worksheet>
 </file>
